--- a/demo/data/каталог-себестоимости.xlsx
+++ b/demo/data/каталог-себестоимости.xlsx
@@ -472,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>276.41</v>
+        <v>304.61</v>
       </c>
       <c r="D2">
         <v>300</v>
@@ -486,7 +486,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>270.5</v>
+        <v>298.1</v>
       </c>
       <c r="D3">
         <v>300</v>
@@ -500,7 +500,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>249.87</v>
+        <v>275.37</v>
       </c>
       <c r="D4">
         <v>300</v>
@@ -514,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>113.65</v>
+        <v>125.25</v>
       </c>
       <c r="D5">
         <v>300</v>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>112.05</v>
+        <v>123.49</v>
       </c>
       <c r="D6">
         <v>300</v>
@@ -542,7 +542,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>110.02</v>
+        <v>121.24</v>
       </c>
       <c r="D7">
         <v>300</v>
@@ -556,7 +556,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>108.22</v>
+        <v>119.26</v>
       </c>
       <c r="D8">
         <v>300</v>
@@ -570,7 +570,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>246.99</v>
+        <v>272.2</v>
       </c>
       <c r="D9">
         <v>300</v>
@@ -584,7 +584,7 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>232.52</v>
+        <v>256.25</v>
       </c>
       <c r="D10">
         <v>300</v>
@@ -598,7 +598,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>319.08</v>
+        <v>351.63</v>
       </c>
       <c r="D11">
         <v>300</v>
@@ -612,7 +612,7 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>312.79</v>
+        <v>344.7</v>
       </c>
       <c r="D12">
         <v>300</v>
@@ -626,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>663.38</v>
+        <v>719.83</v>
       </c>
       <c r="D13">
         <v>300</v>
@@ -640,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>604.3099999999999</v>
+        <v>655.73</v>
       </c>
       <c r="D14">
         <v>300</v>
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>654.8</v>
+        <v>710.52</v>
       </c>
       <c r="D15">
         <v>300</v>
@@ -668,7 +668,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>339.5</v>
+        <v>368.39</v>
       </c>
       <c r="D16">
         <v>300</v>
@@ -682,7 +682,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>333.39</v>
+        <v>361.76</v>
       </c>
       <c r="D17">
         <v>300</v>
@@ -696,7 +696,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>344.43</v>
+        <v>373.74</v>
       </c>
       <c r="D18">
         <v>300</v>
@@ -710,7 +710,7 @@
         <v>11</v>
       </c>
       <c r="C19">
-        <v>289</v>
+        <v>313.59</v>
       </c>
       <c r="D19">
         <v>300</v>
@@ -724,7 +724,7 @@
         <v>11</v>
       </c>
       <c r="C20">
-        <v>298.82</v>
+        <v>324.25</v>
       </c>
       <c r="D20">
         <v>300</v>
@@ -738,7 +738,7 @@
         <v>11</v>
       </c>
       <c r="C21">
-        <v>295.84</v>
+        <v>321.02</v>
       </c>
       <c r="D21">
         <v>300</v>
@@ -752,7 +752,7 @@
         <v>12</v>
       </c>
       <c r="C22">
-        <v>531.41</v>
+        <v>576.64</v>
       </c>
       <c r="D22">
         <v>300</v>
@@ -766,7 +766,7 @@
         <v>12</v>
       </c>
       <c r="C23">
-        <v>518.84</v>
+        <v>563.01</v>
       </c>
       <c r="D23">
         <v>300</v>
@@ -780,7 +780,7 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>533.78</v>
+        <v>579.21</v>
       </c>
       <c r="D24">
         <v>300</v>
@@ -794,7 +794,7 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>301.78</v>
+        <v>327.47</v>
       </c>
       <c r="D25">
         <v>300</v>
@@ -808,7 +808,7 @@
         <v>13</v>
       </c>
       <c r="C26">
-        <v>276.57</v>
+        <v>300.12</v>
       </c>
       <c r="D26">
         <v>300</v>
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="C27">
-        <v>263.71</v>
+        <v>286.16</v>
       </c>
       <c r="D27">
         <v>300</v>
@@ -836,7 +836,7 @@
         <v>14</v>
       </c>
       <c r="C28">
-        <v>254.83</v>
+        <v>276.52</v>
       </c>
       <c r="D28">
         <v>300</v>
@@ -850,7 +850,7 @@
         <v>14</v>
       </c>
       <c r="C29">
-        <v>255.18</v>
+        <v>276.9</v>
       </c>
       <c r="D29">
         <v>300</v>
@@ -864,7 +864,7 @@
         <v>15</v>
       </c>
       <c r="C30">
-        <v>228.98</v>
+        <v>248.47</v>
       </c>
       <c r="D30">
         <v>300</v>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
       <c r="C31">
-        <v>223.74</v>
+        <v>242.77</v>
       </c>
       <c r="D31">
         <v>300</v>
@@ -892,7 +892,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>215.14</v>
+        <v>233.44</v>
       </c>
       <c r="D32">
         <v>300</v>
